--- a/pinn/LED_options.xlsx
+++ b/pinn/LED_options.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\userlisv\Documents\Kevin\Journal simulations\simulation_VLP\pinn\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Owner\Documents\UVSQ\simulation_VLP\pinn\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BBB7E347-72A1-4523-A0C9-5625D18DE5D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B293E1C9-580D-4363-9DE2-86B437F8C7CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{B7655BC0-4001-4F81-BDF6-E462B949D9CB}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="39">
   <si>
     <t>SFH 4725S</t>
   </si>
@@ -190,6 +190,27 @@
       </rPr>
       <t>; justo lo que describes como “azimuth”.</t>
     </r>
+  </si>
+  <si>
+    <t>https://www.digikey.fr/en/products/detail/lumileds/L1I0-0940090000000/7243416</t>
+  </si>
+  <si>
+    <t>FILTRADOS CON CORRIENTE Y VOLTAJE APROPIADOS ADEMAS DE POTENCIA</t>
+  </si>
+  <si>
+    <t>https://otmm.lumileds.com/adaptivemedia/4db181d014ba1e48786177eb6425dcce6fa7be5c</t>
+  </si>
+  <si>
+    <t>https://www.digikey.fr/en/products/detail/ams-osram-usa-inc/SFH-4726S/5231488?utm_source=chatgpt.com</t>
+  </si>
+  <si>
+    <t>https://www.digikey.fr/en/products/detail/ams-osram-usa-inc/LZ1-00R702-0000/4976847?utm_source=chatgpt.com</t>
+  </si>
+  <si>
+    <t>https://www.digikey.fr/en/products/detail/ams-osram-usa-inc/SFH-4725S/3767471?utm_source=chatgpt.com</t>
+  </si>
+  <si>
+    <t>https://www.digikey.fr/en/products/filter/led-emitters-infrared-uv-visible/94?s=N4IgjCBcoCwAxVAYygMwIYBsDOBTANCAPZQDaIAzHAEwUzUiFVgDscAHCALqEAOALlBABlfgCcAlgDsA5iAC%2BhAGwBORCBSQMOAsTIh4Kike59BkEeOlzF4dhXWbteQiUjkKAVnarPpkAJCopKyCoQs1AzQGmhYLnruBuwsKrSMIErskTTp9GwwMOnUKexgCIQwKmBg7H4VxXAwSuksLD51ICksShA8AeaWITaEALRRyFDiAK66buR%2BXPJLQA</t>
   </si>
 </sst>
 </file>
@@ -738,7 +759,7 @@
       <c r="C8" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="D8" s="3" t="s">
+      <c r="D8" s="6" t="s">
         <v>3</v>
       </c>
       <c r="E8" s="3"/>
@@ -792,7 +813,9 @@
     </row>
     <row r="14" spans="1:7" s="4" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="3"/>
-      <c r="B14" s="3"/>
+      <c r="B14" s="3" t="s">
+        <v>33</v>
+      </c>
       <c r="C14" s="3"/>
       <c r="D14" s="3"/>
       <c r="E14" s="3"/>
@@ -802,14 +825,20 @@
       <c r="A15" s="3"/>
       <c r="B15" s="3"/>
       <c r="C15" s="3"/>
-      <c r="D15" s="1"/>
-      <c r="E15" s="3"/>
+      <c r="D15" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E15" s="6" t="s">
+        <v>34</v>
+      </c>
     </row>
     <row r="16" spans="1:7" s="4" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="3"/>
       <c r="B16" s="3"/>
       <c r="C16" s="3"/>
-      <c r="D16" s="3"/>
+      <c r="D16" s="6" t="s">
+        <v>35</v>
+      </c>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
     </row>
@@ -817,7 +846,9 @@
       <c r="A17" s="3"/>
       <c r="B17" s="3"/>
       <c r="C17" s="3"/>
-      <c r="D17" s="3"/>
+      <c r="D17" s="3" t="s">
+        <v>36</v>
+      </c>
       <c r="E17" s="3"/>
       <c r="F17" s="3"/>
     </row>
@@ -825,7 +856,9 @@
       <c r="A18" s="3"/>
       <c r="B18" s="3"/>
       <c r="C18" s="3"/>
-      <c r="D18" s="3"/>
+      <c r="D18" s="3" t="s">
+        <v>37</v>
+      </c>
       <c r="E18" s="3"/>
       <c r="F18" s="3"/>
     </row>
@@ -833,7 +866,9 @@
       <c r="A19" s="3"/>
       <c r="B19" s="3"/>
       <c r="C19" s="3"/>
-      <c r="D19" s="3"/>
+      <c r="D19" s="3" t="s">
+        <v>38</v>
+      </c>
       <c r="E19" s="3"/>
       <c r="F19" s="3"/>
     </row>
@@ -889,6 +924,9 @@
   <hyperlinks>
     <hyperlink ref="D4" r:id="rId1" xr:uid="{85EED62C-2412-45C0-BF39-8F818264B9AB}"/>
     <hyperlink ref="D5" r:id="rId2" xr:uid="{734B8A3B-BC38-4D3D-9800-C7E968FA6522}"/>
+    <hyperlink ref="D8" r:id="rId3" xr:uid="{58E1D2CA-5AAC-471A-8A8D-5612BBE32D3D}"/>
+    <hyperlink ref="E15" r:id="rId4" xr:uid="{05DE4771-4232-4445-B6EE-9A043FF2C42E}"/>
+    <hyperlink ref="D16" r:id="rId5" xr:uid="{4E2FA09A-F85C-47FE-87CA-F5CF3B0D5CD6}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
